--- a/AAII_Financials/Quarterly/DANOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DANOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="92">
   <si>
     <t>DANOY</t>
   </si>
@@ -656,170 +656,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -862,80 +870,86 @@
       <c r="P8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S8" s="3">
         <v>14400300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>6766100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>13492700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>6631600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>12521400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>5774700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>11401300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>6041600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>13297100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>7047800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>14754900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>7862000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>14879100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>7342300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>14375800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>6851600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>13842800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>6681300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>14150500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>7241300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>13688300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>6447700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>12785100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>6499400</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -978,80 +992,86 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3">
         <v>7722700</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3">
         <v>7122500</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="3">
         <v>6549000</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3">
         <v>5950500</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3">
         <v>6873800</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3">
         <v>7484300</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3">
         <v>7607800</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3">
         <v>7490100</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI9" s="3">
         <v>7085300</v>
       </c>
-      <c r="AH9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="3">
         <v>7217800</v>
       </c>
-      <c r="AJ9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="3">
         <v>6953000</v>
       </c>
-      <c r="AL9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO9" s="3">
         <v>6275200</v>
       </c>
-      <c r="AN9" s="3" t="s">
+      <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1094,80 +1114,86 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3">
         <v>6677600</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3">
         <v>6370200</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="3">
         <v>5972400</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3">
         <v>5450800</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3">
         <v>6423300</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3">
         <v>7270600</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3">
         <v>7271300</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3">
         <v>6885700</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI10" s="3">
         <v>6757500</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="3">
         <v>6932800</v>
       </c>
-      <c r="AJ10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="3">
         <v>6735300</v>
       </c>
-      <c r="AL10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="3">
         <v>6510000</v>
       </c>
-      <c r="AN10" s="3" t="s">
+      <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,8 +1234,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1252,80 +1280,86 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3">
         <v>167500</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U12" s="3">
         <v>186500</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W12" s="3">
         <v>175600</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y12" s="3">
         <v>165600</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA12" s="3">
         <v>171300</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC12" s="3">
         <v>212500</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE12" s="3">
         <v>198800</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG12" s="3">
         <v>203500</v>
       </c>
-      <c r="AF12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI12" s="3">
         <v>180500</v>
       </c>
-      <c r="AH12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK12" s="3">
         <v>202000</v>
       </c>
-      <c r="AJ12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM12" s="3">
         <v>181800</v>
       </c>
-      <c r="AL12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO12" s="3">
         <v>208900</v>
       </c>
-      <c r="AN12" s="3" t="s">
+      <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1474,14 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1484,80 +1524,86 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>245300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>412000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>740600</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>395000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3">
         <v>134200</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3">
         <v>344400</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="3">
         <v>369400</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="3">
         <v>150200</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI14" s="3">
         <v>766500</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK14" s="3">
         <v>-486900</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM14" s="3">
         <v>99900</v>
       </c>
-      <c r="AL14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AN14" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP14" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1600,11 +1646,11 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1672,8 +1718,14 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,8 +1763,10 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1755,80 +1809,86 @@
       <c r="P17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>12902500</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" s="3">
         <v>11968500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="3">
         <v>11621100</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3">
         <v>10186400</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="3">
         <v>11573500</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC17" s="3">
         <v>12777300</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="3">
         <v>13063900</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="3">
         <v>12422800</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI17" s="3">
         <v>12633300</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK17" s="3">
         <v>11824700</v>
       </c>
-      <c r="AJ17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM17" s="3">
         <v>11872900</v>
       </c>
-      <c r="AL17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO17" s="3">
         <v>11113600</v>
       </c>
-      <c r="AN17" s="3" t="s">
+      <c r="AP17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1871,80 +1931,86 @@
       <c r="P18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>1497900</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3">
         <v>1524200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>900400</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
         <v>1214800</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="3">
         <v>1723600</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="3">
         <v>1977600</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="3">
         <v>1815200</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="3">
         <v>1953000</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI18" s="3">
         <v>1209500</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK18" s="3">
         <v>2325900</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM18" s="3">
         <v>1815400</v>
       </c>
-      <c r="AL18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO18" s="3">
         <v>1671500</v>
       </c>
-      <c r="AN18" s="3" t="s">
+      <c r="AP18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,8 +2051,10 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2029,80 +2097,86 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
         <v>17300</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="3">
         <v>29300</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>36000</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3">
         <v>33900</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="3">
         <v>15300</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="3">
         <v>5800</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE20" s="3">
         <v>29400</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG20" s="3">
         <v>33100</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI20" s="3">
         <v>16600</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-19100</v>
       </c>
-      <c r="AJ20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM20" s="3">
         <v>35900</v>
       </c>
-      <c r="AL20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AN20" s="3" t="s">
+      <c r="AP20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2151,74 +2225,80 @@
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3">
         <v>2924900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>2697000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3">
         <v>2821600</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>2630400</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>2585800</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="3">
         <v>2437800</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="3">
         <v>2964300</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM21" s="3">
         <v>2286600</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO21" s="3">
         <v>2116400</v>
       </c>
-      <c r="AN21" s="3" t="s">
+      <c r="AP21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2261,80 +2341,86 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="3">
         <v>176200</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="3">
         <v>173500</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>172500</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>173500</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
         <v>200700</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3">
         <v>225300</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE22" s="3">
         <v>243500</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG22" s="3">
         <v>238900</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI22" s="3">
         <v>211600</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK22" s="3">
         <v>203100</v>
       </c>
-      <c r="AJ22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM22" s="3">
         <v>261400</v>
       </c>
-      <c r="AL22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO22" s="3">
         <v>181900</v>
       </c>
-      <c r="AN22" s="3" t="s">
+      <c r="AP22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2377,80 +2463,86 @@
       <c r="P23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>1339000</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="3">
         <v>1380100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="3">
         <v>763900</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="3">
         <v>1075200</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="3">
         <v>1538200</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC23" s="3">
         <v>1758100</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="3">
         <v>1601100</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG23" s="3">
         <v>1747100</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI23" s="3">
         <v>1014600</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK23" s="3">
         <v>2103700</v>
       </c>
-      <c r="AJ23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM23" s="3">
         <v>1589900</v>
       </c>
-      <c r="AL23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO23" s="3">
         <v>1486000</v>
       </c>
-      <c r="AN23" s="3" t="s">
+      <c r="AP23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2493,80 +2585,86 @@
       <c r="P24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>406300</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" s="3">
         <v>402200</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3">
         <v>230600</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="3">
         <v>383000</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="3">
         <v>412400</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC24" s="3">
         <v>544000</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="3">
         <v>384700</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="3">
         <v>359600</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI24" s="3">
         <v>456300</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK24" s="3">
         <v>461100</v>
       </c>
-      <c r="AJ24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM24" s="3">
         <v>483600</v>
       </c>
-      <c r="AL24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO24" s="3">
         <v>464800</v>
       </c>
-      <c r="AN24" s="3" t="s">
+      <c r="AP24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,8 +2779,14 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2725,80 +2829,86 @@
       <c r="P26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3">
         <v>932600</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="3">
         <v>977900</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="3">
         <v>533200</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="3">
         <v>692200</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="3">
         <v>1125800</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC26" s="3">
         <v>1214100</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE26" s="3">
         <v>1216400</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG26" s="3">
         <v>1387500</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI26" s="3">
         <v>558200</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK26" s="3">
         <v>1642600</v>
       </c>
-      <c r="AJ26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM26" s="3">
         <v>1106300</v>
       </c>
-      <c r="AL26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO26" s="3">
         <v>1021200</v>
       </c>
-      <c r="AN26" s="3" t="s">
+      <c r="AP26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2841,80 +2951,86 @@
       <c r="P27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
         <v>791100</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="3">
         <v>908500</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="3">
         <v>1121500</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="3">
         <v>931600</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA27" s="3">
         <v>1098500</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC27" s="3">
         <v>1036700</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE27" s="3">
         <v>1208200</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG27" s="3">
         <v>1346100</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI27" s="3">
         <v>1325800</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK27" s="3">
         <v>1651600</v>
       </c>
-      <c r="AJ27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM27" s="3">
         <v>1093900</v>
       </c>
-      <c r="AL27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO27" s="3">
         <v>986000</v>
       </c>
-      <c r="AN27" s="3" t="s">
+      <c r="AP27" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3145,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3073,11 +3195,11 @@
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -3145,8 +3267,14 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3389,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,8 +3511,14 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3421,80 +3561,86 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
         <v>-17300</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="3">
         <v>-29300</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>-36000</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-33900</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-5800</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-29400</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-33100</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-16600</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK32" s="3">
         <v>19100</v>
       </c>
-      <c r="AJ32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM32" s="3">
         <v>-35900</v>
       </c>
-      <c r="AL32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO32" s="3">
         <v>3500</v>
       </c>
-      <c r="AN32" s="3" t="s">
+      <c r="AP32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3537,80 +3683,86 @@
       <c r="P33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3">
         <v>791100</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3">
         <v>908500</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3">
         <v>1121500</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="3">
         <v>931600</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="3">
         <v>1098500</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC33" s="3">
         <v>1036700</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE33" s="3">
         <v>1208200</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG33" s="3">
         <v>1346100</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI33" s="3">
         <v>1325800</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK33" s="3">
         <v>1651600</v>
       </c>
-      <c r="AJ33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM33" s="3">
         <v>1093900</v>
       </c>
-      <c r="AL33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO33" s="3">
         <v>986000</v>
       </c>
-      <c r="AN33" s="3" t="s">
+      <c r="AP33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,8 +3877,14 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3769,201 +3927,213 @@
       <c r="P35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3">
         <v>791100</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="3">
         <v>908500</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3">
         <v>1121500</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y35" s="3">
         <v>931600</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA35" s="3">
         <v>1098500</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC35" s="3">
         <v>1036700</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE35" s="3">
         <v>1208200</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG35" s="3">
         <v>1346100</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI35" s="3">
         <v>1325800</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK35" s="3">
         <v>1651600</v>
       </c>
-      <c r="AJ35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM35" s="3">
         <v>1093900</v>
       </c>
-      <c r="AL35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO35" s="3">
         <v>986000</v>
       </c>
-      <c r="AN35" s="3" t="s">
+      <c r="AP35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4174,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,56 +4218,58 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2129600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2149200</v>
+      </c>
+      <c r="F41" s="3">
         <v>2328300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2326600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1901400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1749900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1527100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1645100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2205100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2220300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2611900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2501100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2052400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2042600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1123200</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
@@ -4120,98 +4294,104 @@
       <c r="Z41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3">
         <v>751800</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="3">
         <v>888200</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" s="3">
         <v>992500</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI41" s="3">
         <v>775300</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK41" s="3">
         <v>715800</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM41" s="3">
         <v>840400</v>
       </c>
-      <c r="AL41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO41" s="3">
         <v>653800</v>
       </c>
-      <c r="AN41" s="3" t="s">
+      <c r="AP41" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7397500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>7465700</v>
+      </c>
+      <c r="F42" s="3">
         <v>5386900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>5383100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>5162700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>4751400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>4850400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>5225300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>4507700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>4538800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>4021200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>3850600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>3686700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>3669100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>3880500</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>5</v>
       </c>
@@ -4236,98 +4416,104 @@
       <c r="Z42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AA42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC42" s="3">
         <v>4238900</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE42" s="3">
         <v>5093800</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG42" s="3">
         <v>4967000</v>
       </c>
-      <c r="AF42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI42" s="3">
         <v>5567900</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK42" s="3">
         <v>3884300</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM42" s="3">
         <v>3320000</v>
       </c>
-      <c r="AL42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO42" s="3">
         <v>15333500</v>
       </c>
-      <c r="AN42" s="3" t="s">
+      <c r="AP42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3873000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3908700</v>
+      </c>
+      <c r="F43" s="3">
         <v>4515700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4512500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>3783900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3482500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>4037700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>4349800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3503700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3527900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>4210200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>4031500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>3548000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3531100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>4426600</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
@@ -4352,98 +4538,104 @@
       <c r="Z43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3">
         <v>3399500</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="3">
         <v>3645700</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="3">
         <v>3196200</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI43" s="3">
         <v>3175500</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK43" s="3">
         <v>3150500</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM43" s="3">
         <v>3261600</v>
       </c>
-      <c r="AL43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO43" s="3">
         <v>2983800</v>
       </c>
-      <c r="AN43" s="3" t="s">
+      <c r="AP43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2932700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2959800</v>
+      </c>
+      <c r="F44" s="3">
         <v>2729800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2727900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2675300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2462200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2357400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2539600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2640100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2658300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2587600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2477800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>3048000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>3033500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>2799000</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
@@ -4468,98 +4660,104 @@
       <c r="Z44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3">
         <v>2256600</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="3">
         <v>2284600</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG44" s="3">
         <v>2116200</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI44" s="3">
         <v>2033600</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK44" s="3">
         <v>1871500</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM44" s="3">
         <v>1947800</v>
       </c>
-      <c r="AL44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO44" s="3">
         <v>1619900</v>
       </c>
-      <c r="AN44" s="3" t="s">
+      <c r="AP44" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2009600</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2028100</v>
+      </c>
+      <c r="F45" s="3">
         <v>573000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>572600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1623000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1493700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>464900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>500800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1391800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1401400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>845600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>809700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1561100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1553700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>758800</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
@@ -4584,98 +4782,104 @@
       <c r="Z45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3">
         <v>1165100</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="3">
         <v>1344600</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG45" s="3">
         <v>952200</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI45" s="3">
         <v>1397800</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK45" s="3">
         <v>1184800</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM45" s="3">
         <v>1803000</v>
       </c>
-      <c r="AL45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO45" s="3">
         <v>1844100</v>
       </c>
-      <c r="AN45" s="3" t="s">
+      <c r="AP45" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18342300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>18511500</v>
+      </c>
+      <c r="F46" s="3">
         <v>15533600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>15522700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>15146200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>13939700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>13237400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>14260500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>14248400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>14346700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>14276600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>13670600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>13896300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>13829900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>12988100</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
@@ -4700,98 +4904,104 @@
       <c r="Z46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3">
         <v>11811900</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE46" s="3">
         <v>13256900</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG46" s="3">
         <v>12224100</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI46" s="3">
         <v>12950100</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK46" s="3">
         <v>10807000</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM46" s="3">
         <v>11172800</v>
       </c>
-      <c r="AL46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO46" s="3">
         <v>22435000</v>
       </c>
-      <c r="AN46" s="3" t="s">
+      <c r="AP46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1071600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1081500</v>
+      </c>
+      <c r="F47" s="3">
         <v>1776400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1775200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1185000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>1090600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>1368700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1474500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>963200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>969900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1250100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1197100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1015300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1010400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1353000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
@@ -4816,98 +5026,104 @@
       <c r="Z47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>2961700</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="3">
         <v>3069200</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
         <v>2817700</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI47" s="3">
         <v>2636100</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK47" s="3">
         <v>3296400</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM47" s="3">
         <v>3342400</v>
       </c>
-      <c r="AL47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO47" s="3">
         <v>3543700</v>
       </c>
-      <c r="AN47" s="3" t="s">
+      <c r="AP47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7451200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>7519900</v>
+      </c>
+      <c r="F48" s="3">
         <v>7567200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>7561900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>7371700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>6784500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>6749100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>7270800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>6783500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>6830300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>7119500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6817300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>7220500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>7186000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>7216000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4932,98 +5148,104 @@
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>7989800</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>7907800</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>7304400</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI48" s="3">
         <v>6677700</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK48" s="3">
         <v>6737500</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM48" s="3">
         <v>6699400</v>
       </c>
-      <c r="AL48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO48" s="3">
         <v>5911300</v>
       </c>
-      <c r="AN48" s="3" t="s">
+      <c r="AP48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>27244400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>27495700</v>
+      </c>
+      <c r="F49" s="3">
         <v>27164500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>27145400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>26230200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>24140700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>24855600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>26776700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>25256600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>25431000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>25526700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>24443300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>26124500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>25999600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>25904700</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
@@ -5048,50 +5270,56 @@
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3">
         <v>28955300</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="3">
         <v>28937100</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG49" s="3">
         <v>28916000</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI49" s="3">
         <v>26982200</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK49" s="3">
         <v>27988000</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM49" s="3">
         <v>28863200</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO49" s="3">
         <v>18549700</v>
       </c>
-      <c r="AN49" s="3" t="s">
+      <c r="AP49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5434,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,56 +5556,62 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>56500</v>
+      </c>
+      <c r="F52" s="3">
         <v>240700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>240500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>110400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>101600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>127300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>137200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>163600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>156600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>8700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>8700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>133600</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5396,50 +5636,56 @@
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>1237500</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>1268200</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>994800</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI52" s="3">
         <v>848400</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK52" s="3">
         <v>829200</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM52" s="3">
         <v>1161300</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO52" s="3">
         <v>1148000</v>
       </c>
-      <c r="AN52" s="3" t="s">
+      <c r="AP52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,56 +5800,62 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>55551200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>56063600</v>
+      </c>
+      <c r="F54" s="3">
         <v>52918900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>52881600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>51387000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>47293600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>46891000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>50515300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>48635000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>48970800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>49172100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>47085100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>49611400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>49374200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>48392600</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
@@ -5628,50 +5880,56 @@
       <c r="Z54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3">
         <v>52956100</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE54" s="3">
         <v>54439100</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG54" s="3">
         <v>52257000</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI54" s="3">
         <v>50094500</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK54" s="3">
         <v>49658200</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM54" s="3">
         <v>51239000</v>
       </c>
-      <c r="AL54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO54" s="3">
         <v>51587800</v>
       </c>
-      <c r="AN54" s="3" t="s">
+      <c r="AP54" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5970,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,56 +6014,58 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6594300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>6655100</v>
+      </c>
+      <c r="F57" s="3">
         <v>6364900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>6360400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>6323000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>5819300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>5328700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>5740600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5523400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>5561500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>5282400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5058200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5527300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5500900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5235700</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
@@ -5828,98 +6090,104 @@
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>4621800</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>4890300</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>4347200</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI57" s="3">
         <v>4589900</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK57" s="3">
         <v>4380200</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM57" s="3">
         <v>4567600</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO57" s="3">
         <v>4427600</v>
       </c>
-      <c r="AN57" s="3" t="s">
+      <c r="AP57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7430600</v>
+      </c>
+      <c r="E58" s="3">
+        <v>7499100</v>
+      </c>
+      <c r="F58" s="3">
         <v>5923400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>5919300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>5180300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>4767600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>4790400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>5160600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>6393400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>6437600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>6115800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>5856300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>5833000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>5805100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3877300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
@@ -5944,98 +6212,104 @@
       <c r="Z58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>4665000</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="3">
         <v>5073800</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3">
         <v>3572400</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI58" s="3">
         <v>3885500</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK58" s="3">
         <v>3616200</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM58" s="3">
         <v>3953900</v>
       </c>
-      <c r="AL58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO58" s="3">
         <v>2486100</v>
       </c>
-      <c r="AN58" s="3" t="s">
+      <c r="AP58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4937700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4983300</v>
+      </c>
+      <c r="F59" s="3">
         <v>919300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>918700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4487400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>4129900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>781700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>842100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3674100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3699400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>790300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>756800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3922500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3903700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>606000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6060,98 +6334,104 @@
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3">
         <v>3850100</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE59" s="3">
         <v>3977400</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG59" s="3">
         <v>3868100</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI59" s="3">
         <v>3838900</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK59" s="3">
         <v>3739600</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM59" s="3">
         <v>4233300</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO59" s="3">
         <v>3709200</v>
       </c>
-      <c r="AN59" s="3" t="s">
+      <c r="AP59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18962600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>19137600</v>
+      </c>
+      <c r="F60" s="3">
         <v>17171500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>17159500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>15990600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>14716800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>14216800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>15315600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>15590900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>15698600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>15454800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>14798900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>15282800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>15209700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>12963600</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
@@ -6176,98 +6456,104 @@
       <c r="Z60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3">
         <v>13136900</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE60" s="3">
         <v>13941500</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG60" s="3">
         <v>11787600</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI60" s="3">
         <v>12314300</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK60" s="3">
         <v>11734900</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM60" s="3">
         <v>12754800</v>
       </c>
-      <c r="AL60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO60" s="3">
         <v>10623000</v>
       </c>
-      <c r="AN60" s="3" t="s">
+      <c r="AP60" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12479200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>12594300</v>
+      </c>
+      <c r="F61" s="3">
         <v>11826900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>11818600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>12675300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>11665600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>10534200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>11348400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>11091800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>11168400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>11871300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>11367500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>12185600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>12127300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>12010300</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -6293,97 +6579,103 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>15029200</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>16862500</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>16887100</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>16867600</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
         <v>17423400</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="3">
         <v>19803100</v>
       </c>
-      <c r="AL61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="3">
         <v>21642700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1348100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1360500</v>
+      </c>
+      <c r="F62" s="3">
         <v>1413600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1412600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1294200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1191100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1222700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1317200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1469000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1479100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1304300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1248900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1501100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1493900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1702500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
@@ -6408,50 +6700,56 @@
       <c r="Z62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3">
         <v>4502700</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE62" s="3">
         <v>4397400</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG62" s="3">
         <v>4094000</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI62" s="3">
         <v>4019500</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK62" s="3">
         <v>5325000</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM62" s="3">
         <v>4617000</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO62" s="3">
         <v>3834800</v>
       </c>
-      <c r="AN62" s="3" t="s">
+      <c r="AP62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6864,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6986,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,56 +7108,62 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>35342200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>35668200</v>
+      </c>
+      <c r="F66" s="3">
         <v>32995200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>32972000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>32690500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>30086500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>28406700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>30602300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>30637500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>30849100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>31241300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>29915300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>31559000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>31408100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>29164300</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
@@ -6872,50 +7188,56 @@
       <c r="Z66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>32828700</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>35383800</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG66" s="3">
         <v>32923700</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI66" s="3">
         <v>33310000</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK66" s="3">
         <v>33438700</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM66" s="3">
         <v>37260200</v>
       </c>
-      <c r="AL66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO66" s="3">
         <v>36200300</v>
       </c>
-      <c r="AN66" s="3" t="s">
+      <c r="AP66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7278,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7396,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7518,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7640,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,56 +7762,62 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>20003400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>20187900</v>
+      </c>
+      <c r="F72" s="3">
         <v>20642200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>20627700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>19646500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>18081500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>18165400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>19569500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>17359900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>17479800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>18619400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>17829200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>18052400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>17966100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>19147200</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
@@ -7494,50 +7842,56 @@
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>17792500</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>16894300</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>18803400</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI72" s="3">
         <v>16240700</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK72" s="3">
         <v>16467400</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM72" s="3">
         <v>13438100</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO72" s="3">
         <v>14126800</v>
       </c>
-      <c r="AN72" s="3" t="s">
+      <c r="AP72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8006,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8128,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,56 +8250,62 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20117700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>20303200</v>
+      </c>
+      <c r="F76" s="3">
         <v>19862600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>19848600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>18628300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>17144400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>18423200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>19847200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>17938500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>18062400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>17880000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>17121100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>18015300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>17929200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>19154600</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
@@ -7958,50 +8330,56 @@
       <c r="Z76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3">
         <v>20127300</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE76" s="3">
         <v>19055300</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG76" s="3">
         <v>19333300</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI76" s="3">
         <v>16784600</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK76" s="3">
         <v>16219500</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM76" s="3">
         <v>13978900</v>
       </c>
-      <c r="AL76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO76" s="3">
         <v>15387500</v>
       </c>
-      <c r="AN76" s="3" t="s">
+      <c r="AP76" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,129 +8494,141 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8281,80 +8671,86 @@
       <c r="P81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
         <v>791100</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U81" s="3">
         <v>908500</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W81" s="3">
         <v>1121500</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="3">
         <v>931600</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="3">
         <v>1098500</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC81" s="3">
         <v>1036700</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE81" s="3">
         <v>1208200</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG81" s="3">
         <v>1346100</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI81" s="3">
         <v>1325800</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK81" s="3">
         <v>1651600</v>
       </c>
-      <c r="AJ81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM81" s="3">
         <v>1093900</v>
       </c>
-      <c r="AL81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO81" s="3">
         <v>986000</v>
       </c>
-      <c r="AN81" s="3" t="s">
+      <c r="AP81" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8791,132 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>306500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>282100</v>
+      </c>
+      <c r="F83" s="3">
         <v>191000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>205800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>295700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>297800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>449300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>430200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>290900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>289500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>181700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>166700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>335000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>356000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>213800</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
         <v>1371400</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1448200</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="3">
         <v>838200</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE83" s="3">
         <v>785800</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG83" s="3">
         <v>599700</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI83" s="3">
         <v>1211700</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK83" s="3">
         <v>657500</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM83" s="3">
         <v>435300</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO83" s="3">
         <v>448400</v>
       </c>
-      <c r="AN83" s="3" t="s">
+      <c r="AP83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9031,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9153,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9275,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9397,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9519,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>718600</v>
+      </c>
+      <c r="E89" s="3">
+        <v>725200</v>
+      </c>
+      <c r="F89" s="3">
         <v>1326800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1325800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>892000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>820900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1204600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1297700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>805700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>811300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1115300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1068000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>777300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>773600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1065500</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S89" s="3">
+        <v>0</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
         <v>3766200</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W89" s="3">
+        <v>0</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
         <v>2959300</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="3">
         <v>2345300</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3">
         <v>1688100</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>1993200</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI89" s="3">
         <v>1579400</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK89" s="3">
         <v>1972500</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM89" s="3">
         <v>1345300</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO89" s="3">
         <v>1855800</v>
       </c>
-      <c r="AN89" s="3" t="s">
+      <c r="AP89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9689,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-236500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-238700</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-400100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-219000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-201600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-312700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-336800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-170900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-172100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-296800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-284200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-169200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-168400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-296600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-581000</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-381000</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-959500</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-691100</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-422300</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-683700</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-402100</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-675400</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-411800</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO91" s="3">
         <v>-665600</v>
       </c>
-      <c r="AN91" s="3" t="s">
+      <c r="AP91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9929,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +10051,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-179900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-181600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-849500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-848900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-191400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-176200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-308000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-331800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>70700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>71200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-320000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-306400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-139200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-138500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-198200</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
         <v>608200</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-608400</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-734300</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-445900</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-720400</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI94" s="3">
         <v>1035600</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-244600</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-12587600</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO94" s="3">
         <v>-700800</v>
       </c>
-      <c r="AN94" s="3" t="s">
+      <c r="AP94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,77 +10221,79 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>822600</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>830200</v>
       </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>809700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>745200</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>722200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>727200</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>698100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>694800</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-1367100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-1359500</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -9836,43 +10304,49 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1477600</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-477400</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-55000</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-41500</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-57500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10461,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10583,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10705,376 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-562100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-567300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-446200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-445900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-499100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-459400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-948900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1022200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-1062900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1070200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-657100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-629200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-473800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-471500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-798300</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
         <v>-4365700</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-2353900</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-1678700</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-1131700</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-1153300</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-2520900</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK100" s="3">
         <v>-2046500</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM100" s="3">
         <v>11346700</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO100" s="3">
         <v>-1124500</v>
       </c>
-      <c r="AN100" s="3" t="s">
+      <c r="AP100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-136800</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-125900</v>
+      </c>
+      <c r="F101" s="3">
         <v>44500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>48000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-47100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-47500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-50300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-48200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-224900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-223800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-22400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-20600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>80500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>85500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>17100</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
         <v>62900</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-47900</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-61900</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-209400</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG101" s="3">
         <v>45000</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-26600</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK101" s="3">
         <v>193000</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM101" s="3">
         <v>112200</v>
       </c>
-      <c r="AL101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO101" s="3">
         <v>-142000</v>
       </c>
-      <c r="AN101" s="3" t="s">
+      <c r="AP101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>18400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-12300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-12300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>64600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>59400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-7800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-8400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-233600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-235200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>87900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>84100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-60600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-60300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>46500</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
         <v>71600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-50900</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-129600</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-98800</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>164400</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI102" s="3">
         <v>67600</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK102" s="3">
         <v>-125700</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM102" s="3">
         <v>216500</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO102" s="3">
         <v>-111500</v>
       </c>
-      <c r="AN102" s="3" t="s">
+      <c r="AP102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
